--- a/SHINHWA_QMS_WORKFLOW/99_산출물/메시지_발송일정표_20261028_v4.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/메시지_발송일정표_20261028_v4.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[IATF 사후심사] 증빙 수집 취합 요청 (직접 정리 12건 + 운영증빙 20영역, 취합 목표 2026-11-06)</t>
+          <t>[IATF 사후심사] 증빙 수집 취합 요청 (직접 정리 13건 + 운영증빙 20영역, 취합 목표 2026-11-06)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>[IATF 사후심사] 부서별 운영증빙 제출 요청 (취합 목표 2026-11-06)</t>
+          <t>[IATF 사후심사] 증빙 수집 취합 요청 (직접 정리 13건 + 운영증빙 20영역, 취합 목표 2026-11-06)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -2843,7 +2843,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
